--- a/data/trans_orig/P6602-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6602-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2007</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2007 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106927</t>
+          <t>108015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144065</t>
+          <t>144534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82353</t>
+          <t>82804</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107833</t>
+          <t>106937</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198722</t>
+          <t>199260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>245655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65560</t>
+          <t>65925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>99428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>47456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95887</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135986</t>
+          <t>136346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127252</t>
+          <t>128176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165166</t>
+          <t>165517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145540</t>
+          <t>145721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>188540</t>
+          <t>187408</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14686</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49937</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211866</t>
+          <t>213044</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>261550</t>
+          <t>261574</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>175501</t>
+          <t>175906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>204481</t>
+          <t>206447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>398450</t>
+          <t>395504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>457380</t>
+          <t>458198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107596</t>
+          <t>105647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149257</t>
+          <t>147392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39031</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65959</t>
+          <t>64387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153933</t>
+          <t>153638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202195</t>
+          <t>203172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116673</t>
+          <t>117551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158389</t>
+          <t>158140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127121</t>
+          <t>129033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173415</t>
+          <t>175944</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45945</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77242</t>
+          <t>77585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54831</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87546</t>
+          <t>88473</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162859</t>
+          <t>160468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203630</t>
+          <t>203358</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>144944</t>
+          <t>145400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169918</t>
+          <t>169525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314859</t>
+          <t>315851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367438</t>
+          <t>364777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76343</t>
+          <t>76965</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111359</t>
+          <t>111140</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>26996</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48904</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>110607</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152283</t>
+          <t>151524</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78064</t>
+          <t>79387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115844</t>
+          <t>114263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89181</t>
+          <t>88082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127607</t>
+          <t>127821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27550</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49641</t>
+          <t>50450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55440</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>273687</t>
+          <t>272073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>320437</t>
+          <t>316473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>282592</t>
+          <t>282368</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316452</t>
+          <t>316874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564749</t>
+          <t>565473</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>624215</t>
+          <t>624936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87371</t>
+          <t>89587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>125522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64018</t>
+          <t>65917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134201</t>
+          <t>136551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181546</t>
+          <t>181818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96139</t>
+          <t>96790</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136159</t>
+          <t>133433</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34126</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>118307</t>
+          <t>115980</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160971</t>
+          <t>160290</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26018</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>39177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66477</t>
+          <t>65456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>797723</t>
+          <t>798405</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>882002</t>
+          <t>887764</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>718098</t>
+          <t>715506</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>775235</t>
+          <t>775725</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1532701</t>
+          <t>1530439</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1644348</t>
+          <t>1638751</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>374236</t>
+          <t>374122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>449896</t>
+          <t>444821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149520</t>
+          <t>147795</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>198504</t>
+          <t>196179</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>534660</t>
+          <t>540036</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>623910</t>
+          <t>630436</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>459004</t>
+          <t>454197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>534147</t>
+          <t>533957</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54221</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85231</t>
+          <t>84907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>517780</t>
+          <t>522576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>607289</t>
+          <t>607850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>138268</t>
+          <t>138700</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>189433</t>
+          <t>190931</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27787</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53185</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>174086</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>229886</t>
+          <t>229033</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2012</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2012 (tasa de respuesta: 99,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60921</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90170</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93732</t>
+          <t>94120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119289</t>
+          <t>119255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163852</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205194</t>
+          <t>203831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>65527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96446</t>
+          <t>97926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50313</t>
+          <t>48648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99181</t>
+          <t>99618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136456</t>
+          <t>136328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51301</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78785</t>
+          <t>81711</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>61880</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93586</t>
+          <t>94860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>34963</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60549</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66351</t>
+          <t>66922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127024</t>
+          <t>128405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167950</t>
+          <t>171981</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153037</t>
+          <t>154002</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>185092</t>
+          <t>185939</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>287285</t>
+          <t>288945</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>344406</t>
+          <t>343841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83415</t>
+          <t>85981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120695</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>46517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75359</t>
+          <t>74877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141467</t>
+          <t>140319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187932</t>
+          <t>187397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67575</t>
+          <t>66160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101179</t>
+          <t>99823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77589</t>
+          <t>78075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116656</t>
+          <t>116664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61126</t>
+          <t>58822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93231</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37824</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>84947</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122900</t>
+          <t>124843</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98379</t>
+          <t>100250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135750</t>
+          <t>137491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109330</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139111</t>
+          <t>140164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218837</t>
+          <t>217840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269024</t>
+          <t>264865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64887</t>
+          <t>64293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97818</t>
+          <t>96889</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>42244</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>68475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>111326</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>155300</t>
+          <t>156492</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64403</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98888</t>
+          <t>100203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81059</t>
+          <t>83878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119876</t>
+          <t>122291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32628</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58069</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>44543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74805</t>
+          <t>75248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>155113</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>195994</t>
+          <t>195805</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>174835</t>
+          <t>174860</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>209933</t>
+          <t>208900</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>340171</t>
+          <t>338853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>395266</t>
+          <t>393184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101230</t>
+          <t>101070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138860</t>
+          <t>139076</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56792</t>
+          <t>57136</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86207</t>
+          <t>88163</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>167433</t>
+          <t>167680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216551</t>
+          <t>215428</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68248</t>
+          <t>66999</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102309</t>
+          <t>100759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>27244</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>80799</t>
+          <t>82459</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>119808</t>
+          <t>120097</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>54062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>32286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47942</t>
+          <t>47025</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>78991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>478421</t>
+          <t>478466</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>554077</t>
+          <t>551632</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>563950</t>
+          <t>563012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>624936</t>
+          <t>625035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1054429</t>
+          <t>1058141</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1154057</t>
+          <t>1154372</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>350398</t>
+          <t>350935</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>417938</t>
+          <t>420555</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>193055</t>
+          <t>197120</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>252989</t>
+          <t>248769</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>564233</t>
+          <t>562787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>651040</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>278197</t>
+          <t>281115</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>344716</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>48959</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78776</t>
+          <t>79520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>336503</t>
+          <t>338249</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>413796</t>
+          <t>411815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>182681</t>
+          <t>181290</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>236428</t>
+          <t>235876</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52144</t>
+          <t>52559</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>86251</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>245603</t>
+          <t>243065</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>307620</t>
+          <t>305498</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2016</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59457</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88859</t>
+          <t>90320</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87896</t>
+          <t>89305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112351</t>
+          <t>113750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155525</t>
+          <t>155979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192582</t>
+          <t>194635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51415</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77484</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26482</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47238</t>
+          <t>46798</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83489</t>
+          <t>84639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118230</t>
+          <t>119402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>33215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57818</t>
+          <t>57261</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>19811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44190</t>
+          <t>43429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71124</t>
+          <t>71249</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>47455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73753</t>
+          <t>74893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63019</t>
+          <t>61966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94031</t>
+          <t>94530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111178</t>
+          <t>113027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152521</t>
+          <t>151216</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137156</t>
+          <t>136509</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>166612</t>
+          <t>168921</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>256589</t>
+          <t>258301</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>312138</t>
+          <t>312661</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95839</t>
+          <t>97470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133687</t>
+          <t>134996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45292</t>
+          <t>45682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71980</t>
+          <t>72024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149700</t>
+          <t>149010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195624</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65821</t>
+          <t>66668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100645</t>
+          <t>99208</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42785</t>
+          <t>43256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90540</t>
+          <t>93777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135278</t>
+          <t>133837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>64762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98124</t>
+          <t>99250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>44754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94787</t>
+          <t>95180</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>136969</t>
+          <t>134311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74572</t>
+          <t>76250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110310</t>
+          <t>110215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>90627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121095</t>
+          <t>121458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172101</t>
+          <t>175092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>222218</t>
+          <t>221653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95794</t>
+          <t>94481</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133160</t>
+          <t>131687</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76511</t>
+          <t>77473</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>107894</t>
+          <t>107564</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>182506</t>
+          <t>183985</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>230898</t>
+          <t>232670</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69211</t>
+          <t>68024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101605</t>
+          <t>101458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40127</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65937</t>
+          <t>64381</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116628</t>
+          <t>115027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159419</t>
+          <t>158077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57048</t>
+          <t>57288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>88690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29633</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75965</t>
+          <t>74227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112426</t>
+          <t>110751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>147976</t>
+          <t>145586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186406</t>
+          <t>185766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>184553</t>
+          <t>183990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>220500</t>
+          <t>219786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>343091</t>
+          <t>339245</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>396484</t>
+          <t>394479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92642</t>
+          <t>94331</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127945</t>
+          <t>129244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57844</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88905</t>
+          <t>89438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>160563</t>
+          <t>160276</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206010</t>
+          <t>208441</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72072</t>
+          <t>73497</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>105559</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44638</t>
+          <t>41671</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99404</t>
+          <t>99365</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140901</t>
+          <t>140239</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23715</t>
+          <t>23687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47325</t>
+          <t>46359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27758</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67361</t>
+          <t>66163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>424056</t>
+          <t>431176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>498353</t>
+          <t>498405</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>528516</t>
+          <t>531373</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>592501</t>
+          <t>593760</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>979881</t>
+          <t>977280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1078947</t>
+          <t>1076980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>370920</t>
+          <t>370376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>436027</t>
+          <t>440275</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>230205</t>
+          <t>233280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>285786</t>
+          <t>286661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>619568</t>
+          <t>619466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>705790</t>
+          <t>706609</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>269618</t>
+          <t>265167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>331319</t>
+          <t>329267</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>105966</t>
+          <t>104652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>150079</t>
+          <t>146172</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>384695</t>
+          <t>390972</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>463219</t>
+          <t>467360</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>221195</t>
+          <t>218950</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>283500</t>
+          <t>279916</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70860</t>
+          <t>72020</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>107268</t>
+          <t>107831</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>302489</t>
+          <t>300820</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>371094</t>
+          <t>371023</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2023</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2023 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51700</t>
+          <t>51792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>77939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90845</t>
+          <t>90661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125329</t>
+          <t>124663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80157</t>
+          <t>79057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23536</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77501</t>
+          <t>77309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113756</t>
+          <t>114774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33467</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60005</t>
+          <t>60397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47143</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76533</t>
+          <t>77608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>16359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>47831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>191494</t>
+          <t>189821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>482104</t>
+          <t>478485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91745</t>
+          <t>91897</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116545</t>
+          <t>116976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>308649</t>
+          <t>308122</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>630435</t>
+          <t>617787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165966</t>
+          <t>167762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71386</t>
+          <t>70739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>61344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225701</t>
+          <t>224827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>23913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130230</t>
+          <t>133028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>37683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142599</t>
+          <t>141397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67972</t>
+          <t>70728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18857</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81376</t>
+          <t>82102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>50679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77683</t>
+          <t>77758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40342</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97310</t>
+          <t>97419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91236</t>
+          <t>96056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160444</t>
+          <t>161464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40724</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68369</t>
+          <t>67633</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>44490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60604</t>
+          <t>60526</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>106281</t>
+          <t>103054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43716</t>
+          <t>42362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101230</t>
+          <t>103002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>45372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163879</t>
+          <t>158320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39016</t>
+          <t>37769</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>23400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51537</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113164</t>
+          <t>113049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145323</t>
+          <t>144383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119955</t>
+          <t>120587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141722</t>
+          <t>142127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>242369</t>
+          <t>240863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>280339</t>
+          <t>280201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40148</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66419</t>
+          <t>66359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44153</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70514</t>
+          <t>70641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102412</t>
+          <t>104086</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25235</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48625</t>
+          <t>48576</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>29161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>19085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21224</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>427917</t>
+          <t>425033</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>833137</t>
+          <t>809277</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>314475</t>
+          <t>301212</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>407674</t>
+          <t>406662</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>814923</t>
+          <t>811912</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1246821</t>
+          <t>1272856</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132617</t>
+          <t>141411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>338963</t>
+          <t>340135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128000</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175796</t>
+          <t>176373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>280571</t>
+          <t>272371</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>491202</t>
+          <t>502412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88046</t>
+          <t>92981</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>226750</t>
+          <t>230537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>198811</t>
+          <t>225911</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174868</t>
+          <t>176958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>352332</t>
+          <t>363820</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>58360</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>142686</t>
+          <t>137669</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37637</t>
+          <t>36973</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>63792</t>
+          <t>62186</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>91761</t>
+          <t>93361</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>184340</t>
+          <t>188182</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6602-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6602-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108015</t>
+          <t>109887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144534</t>
+          <t>144757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82804</t>
+          <t>83821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106937</t>
+          <t>107997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199260</t>
+          <t>196938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245655</t>
+          <t>244528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65925</t>
+          <t>64270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99428</t>
+          <t>97845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47456</t>
+          <t>46281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>98269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136346</t>
+          <t>137659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128176</t>
+          <t>128266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165517</t>
+          <t>167942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>27595</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145721</t>
+          <t>145088</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>187408</t>
+          <t>192750</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42497</t>
+          <t>42076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>50286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213044</t>
+          <t>212012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>261574</t>
+          <t>261429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>175906</t>
+          <t>174007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>206447</t>
+          <t>204715</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>395504</t>
+          <t>400274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>458198</t>
+          <t>460812</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105647</t>
+          <t>106224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147392</t>
+          <t>146938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38277</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64387</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153638</t>
+          <t>154203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203172</t>
+          <t>201871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117551</t>
+          <t>116572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158140</t>
+          <t>159731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129033</t>
+          <t>127637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175944</t>
+          <t>172912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77585</t>
+          <t>75880</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54618</t>
+          <t>54756</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88473</t>
+          <t>87381</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160468</t>
+          <t>162261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203358</t>
+          <t>203097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145400</t>
+          <t>143872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169525</t>
+          <t>169594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315851</t>
+          <t>316590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364777</t>
+          <t>364635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76965</t>
+          <t>76517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111140</t>
+          <t>111920</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>48771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110607</t>
+          <t>111354</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>151524</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79387</t>
+          <t>78814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114263</t>
+          <t>114051</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88082</t>
+          <t>90570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>126705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50450</t>
+          <t>49120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56481</t>
+          <t>55263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>272073</t>
+          <t>274080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>316473</t>
+          <t>318945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>282368</t>
+          <t>284449</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316874</t>
+          <t>317752</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>565473</t>
+          <t>567470</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>624936</t>
+          <t>627085</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89587</t>
+          <t>89945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125522</t>
+          <t>126317</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>37540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65917</t>
+          <t>65311</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136551</t>
+          <t>135786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181818</t>
+          <t>180380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96790</t>
+          <t>97558</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133433</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>115980</t>
+          <t>117470</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160290</t>
+          <t>161571</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>47250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>37254</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65456</t>
+          <t>64153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>798405</t>
+          <t>795684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>887764</t>
+          <t>884966</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>715506</t>
+          <t>712698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>775725</t>
+          <t>776740</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1530439</t>
+          <t>1536867</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1638751</t>
+          <t>1643180</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>374122</t>
+          <t>374513</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>444821</t>
+          <t>446029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196179</t>
+          <t>200366</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>540036</t>
+          <t>539441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>630436</t>
+          <t>624917</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>454197</t>
+          <t>457831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>533957</t>
+          <t>533660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53606</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84907</t>
+          <t>86322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>522576</t>
+          <t>518971</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>607850</t>
+          <t>605853</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>138700</t>
+          <t>137682</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>190931</t>
+          <t>185524</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52400</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>172386</t>
+          <t>175419</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>229033</t>
+          <t>229125</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62203</t>
+          <t>60861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91547</t>
+          <t>90341</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94120</t>
+          <t>94418</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119255</t>
+          <t>119888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161980</t>
+          <t>161203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203831</t>
+          <t>203931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65527</t>
+          <t>67019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97926</t>
+          <t>97422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48648</t>
+          <t>48986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99618</t>
+          <t>99702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136328</t>
+          <t>139366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51258</t>
+          <t>52175</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81711</t>
+          <t>80813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61880</t>
+          <t>60167</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>94949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60881</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38592</t>
+          <t>39557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66922</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128405</t>
+          <t>128375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>171981</t>
+          <t>168621</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>154002</t>
+          <t>153512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>185582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>288945</t>
+          <t>291743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>343841</t>
+          <t>342753</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85981</t>
+          <t>86066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120760</t>
+          <t>121816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46517</t>
+          <t>48534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74877</t>
+          <t>77239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140319</t>
+          <t>142386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187397</t>
+          <t>186435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66160</t>
+          <t>66656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99823</t>
+          <t>100646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>21877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78075</t>
+          <t>78372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116664</t>
+          <t>117305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58822</t>
+          <t>60671</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93089</t>
+          <t>93351</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84947</t>
+          <t>85595</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>121675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100250</t>
+          <t>98965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137491</t>
+          <t>136476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107525</t>
+          <t>109305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140164</t>
+          <t>138944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217840</t>
+          <t>217507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264865</t>
+          <t>268470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64293</t>
+          <t>64738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96889</t>
+          <t>95167</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42244</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68475</t>
+          <t>68438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111326</t>
+          <t>112949</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156492</t>
+          <t>157046</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65773</t>
+          <t>65358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100203</t>
+          <t>97393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>31200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83878</t>
+          <t>82003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122291</t>
+          <t>120061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57392</t>
+          <t>59402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24585</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44543</t>
+          <t>44225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75248</t>
+          <t>74451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>155113</t>
+          <t>155704</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>195805</t>
+          <t>195999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>174860</t>
+          <t>176121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>208900</t>
+          <t>209982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>338853</t>
+          <t>337683</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>393184</t>
+          <t>393298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101070</t>
+          <t>102910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139076</t>
+          <t>139769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57136</t>
+          <t>56675</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88163</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>167680</t>
+          <t>168171</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>215428</t>
+          <t>214446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66999</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100759</t>
+          <t>99903</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27244</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>82459</t>
+          <t>82987</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120097</t>
+          <t>121267</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54062</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47025</t>
+          <t>47214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78991</t>
+          <t>80070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>478466</t>
+          <t>481913</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>551632</t>
+          <t>555724</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>563012</t>
+          <t>560571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>625035</t>
+          <t>624014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1058141</t>
+          <t>1055602</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1154372</t>
+          <t>1156860</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>350935</t>
+          <t>350585</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>420555</t>
+          <t>419527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197120</t>
+          <t>197241</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248769</t>
+          <t>253305</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>562787</t>
+          <t>563294</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>649307</t>
+          <t>653824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>281115</t>
+          <t>279486</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>344716</t>
+          <t>344046</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48959</t>
+          <t>47805</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79520</t>
+          <t>81646</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338249</t>
+          <t>334155</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>411815</t>
+          <t>409781</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>181290</t>
+          <t>180304</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>235876</t>
+          <t>235981</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52559</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>84948</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>243065</t>
+          <t>243685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>305498</t>
+          <t>308595</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>60033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90320</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89305</t>
+          <t>87703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113750</t>
+          <t>112801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155979</t>
+          <t>155503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194635</t>
+          <t>196776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>50035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78184</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>47215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84639</t>
+          <t>83860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119402</t>
+          <t>119158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57261</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43429</t>
+          <t>43703</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71249</t>
+          <t>70403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47455</t>
+          <t>46552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74893</t>
+          <t>74336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61966</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94530</t>
+          <t>95022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113027</t>
+          <t>113509</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151216</t>
+          <t>152953</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>136509</t>
+          <t>136997</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168921</t>
+          <t>169909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>258301</t>
+          <t>259277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>312661</t>
+          <t>313734</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97470</t>
+          <t>95858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134996</t>
+          <t>133012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>44952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72024</t>
+          <t>72508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149010</t>
+          <t>149461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195863</t>
+          <t>195524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66668</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99208</t>
+          <t>101108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>43051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93777</t>
+          <t>95005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133837</t>
+          <t>134472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64762</t>
+          <t>65309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99250</t>
+          <t>99979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23464</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44754</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95180</t>
+          <t>94404</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>134311</t>
+          <t>135982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76250</t>
+          <t>76235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110215</t>
+          <t>111460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90627</t>
+          <t>90540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121458</t>
+          <t>122072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175092</t>
+          <t>173473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221653</t>
+          <t>220982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94481</t>
+          <t>95839</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131687</t>
+          <t>131488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77473</t>
+          <t>76968</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>107564</t>
+          <t>108027</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>183985</t>
+          <t>181679</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>232670</t>
+          <t>234359</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68024</t>
+          <t>67279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101458</t>
+          <t>100072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39351</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64381</t>
+          <t>68268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115027</t>
+          <t>116153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158077</t>
+          <t>160297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57288</t>
+          <t>57232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>89047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28862</t>
+          <t>30335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74227</t>
+          <t>74421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110751</t>
+          <t>112481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145586</t>
+          <t>145710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>185766</t>
+          <t>185242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183990</t>
+          <t>182424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219786</t>
+          <t>219313</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>339245</t>
+          <t>340749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>394479</t>
+          <t>396120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94331</t>
+          <t>94220</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129244</t>
+          <t>129076</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>58286</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89438</t>
+          <t>88188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>160276</t>
+          <t>160654</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208441</t>
+          <t>207366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73497</t>
+          <t>73534</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105559</t>
+          <t>106710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>43267</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>99684</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140239</t>
+          <t>138862</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46359</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66163</t>
+          <t>68251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>431176</t>
+          <t>430428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>498405</t>
+          <t>503593</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>531373</t>
+          <t>530800</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>593760</t>
+          <t>592715</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>977280</t>
+          <t>980826</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1076980</t>
+          <t>1077030</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>370376</t>
+          <t>370830</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>440275</t>
+          <t>440882</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>233280</t>
+          <t>232347</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>286661</t>
+          <t>288144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>619466</t>
+          <t>619668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>706609</t>
+          <t>704335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>265167</t>
+          <t>268039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>329267</t>
+          <t>332760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>104652</t>
+          <t>104456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146172</t>
+          <t>146444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>390972</t>
+          <t>385953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>467360</t>
+          <t>461599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>218950</t>
+          <t>219361</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>279916</t>
+          <t>280657</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>72020</t>
+          <t>70998</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>107831</t>
+          <t>108484</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>300820</t>
+          <t>299652</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>371023</t>
+          <t>369776</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>31130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51792</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69391</t>
+          <t>75366</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59208</t>
+          <t>65680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77939</t>
+          <t>85883</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>107784</t>
+          <t>119552</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90661</t>
+          <t>103081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124663</t>
+          <t>139536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63603</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48829</t>
+          <t>51186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79057</t>
+          <t>80933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>32879</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>24548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39364</t>
+          <t>41614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>94321</t>
+          <t>97971</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77309</t>
+          <t>81814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114774</t>
+          <t>117381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>52800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34735</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>67833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23542</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>61175</t>
+          <t>69245</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>87880</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>31389</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16359</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>44068</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47831</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>353723</t>
+          <t>120006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>189821</t>
+          <t>99406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>478485</t>
+          <t>138713</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104205</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91897</t>
+          <t>97888</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116976</t>
+          <t>125389</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>457929</t>
+          <t>232543</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>308122</t>
+          <t>206369</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>617787</t>
+          <t>256329</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86484</t>
+          <t>94299</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>76917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167762</t>
+          <t>113582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59644</t>
+          <t>66736</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>56299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70739</t>
+          <t>79843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146128</t>
+          <t>161035</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61344</t>
+          <t>139566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224827</t>
+          <t>183592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>76637</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23913</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133028</t>
+          <t>95403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>90118</t>
+          <t>100760</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37683</t>
+          <t>83784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141397</t>
+          <t>122026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34478</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70728</t>
+          <t>57554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>51052</t>
+          <t>59630</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>77312</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>63641</t>
+          <t>67910</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50679</t>
+          <t>52909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77758</t>
+          <t>83391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74137</t>
+          <t>84599</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>73875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97419</t>
+          <t>95509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>137778</t>
+          <t>152509</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96056</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161464</t>
+          <t>171961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53248</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>47325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67633</t>
+          <t>77670</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>39963</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>30133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>84960</t>
+          <t>101120</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>83768</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103054</t>
+          <t>119514</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>38096</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19946</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42362</t>
+          <t>52438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>47831</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103002</t>
+          <t>25601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>78257</t>
+          <t>55534</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45372</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158320</t>
+          <t>73532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37769</t>
+          <t>55369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>47883</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51951</t>
+          <t>66193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>129392</t>
+          <t>141056</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113049</t>
+          <t>125349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>144383</t>
+          <t>157691</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>131372</t>
+          <t>142101</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120587</t>
+          <t>129089</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142127</t>
+          <t>153985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>260764</t>
+          <t>283157</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>240863</t>
+          <t>263026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>280201</t>
+          <t>303261</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52183</t>
+          <t>56445</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39437</t>
+          <t>43088</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66359</t>
+          <t>71986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>37489</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25182</t>
+          <t>27987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>86386</t>
+          <t>93934</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70641</t>
+          <t>77345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104086</t>
+          <t>112735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>42980</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>40731</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24531</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48576</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19085</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42345</t>
+          <t>50175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>186445</t>
+          <t>206949</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186445</t>
+          <t>206949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>186445</t>
+          <t>206949</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>455068</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>455068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>455068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>585150</t>
+          <t>373157</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>425033</t>
+          <t>339559</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>809277</t>
+          <t>405964</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>379104</t>
+          <t>414603</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>301212</t>
+          <t>392298</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>406662</t>
+          <t>437568</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>964255</t>
+          <t>787760</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>811912</t>
+          <t>745799</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1272856</t>
+          <t>830044</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>255518</t>
+          <t>276993</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141411</t>
+          <t>248169</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>340135</t>
+          <t>308811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>156277</t>
+          <t>177068</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>158782</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176373</t>
+          <t>197536</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>411795</t>
+          <t>454061</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>272371</t>
+          <t>415845</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>502412</t>
+          <t>492731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>170548</t>
+          <t>198547</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>92981</t>
+          <t>171168</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>230537</t>
+          <t>228692</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>94048</t>
+          <t>67722</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60063</t>
+          <t>53492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>225911</t>
+          <t>83724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>264595</t>
+          <t>266270</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>176958</t>
+          <t>237953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>363820</t>
+          <t>302718</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>101781</t>
+          <t>129559</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>58360</t>
+          <t>106381</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>137669</t>
+          <t>157400</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>46221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62186</t>
+          <t>74759</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>150688</t>
+          <t>188828</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>93361</t>
+          <t>162060</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>188182</t>
+          <t>221671</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>678335</t>
+          <t>718661</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>678335</t>
+          <t>718661</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>678335</t>
+          <t>718661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1791332</t>
+          <t>1696918</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1791332</t>
+          <t>1696918</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1791332</t>
+          <t>1696918</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
